--- a/data/trans_orig/AIRE_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41573</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81992</t>
+          <t>82589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100001</t>
+          <t>99939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,08%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44387</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>70841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>85176</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108342</t>
+          <t>108408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149490</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176681</t>
+          <t>176327</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46712</t>
+          <t>47066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73903</t>
+          <t>73524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62315</t>
+          <t>62303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88869</t>
+          <t>90301</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56696</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>72465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>126225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158483</t>
+          <t>159916</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>37615</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30807</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>63065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>77592</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>59066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73918</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128756</t>
+          <t>128844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148274</t>
+          <t>147959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24502</t>
+          <t>23786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30678</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>511856</t>
+          <t>510709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>561089</t>
+          <t>560991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>58538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93927</t>
+          <t>91637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89156</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124457</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156602</t>
+          <t>156700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>205835</t>
+          <t>206982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47786</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39924</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>54703</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>41903</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36589</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45964</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>66,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56310</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>91835</t>
+          <t>90052</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82589</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99939</t>
+          <t>98564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20345</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13428</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28207</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12956</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18270</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21588</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>68131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71520</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126379</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>92627</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>78477</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>100667</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>79,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>64816</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>56771</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>70841</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>73,83%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,67%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>99526</t>
+          <t>64158</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85176</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108408</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>164342</t>
+          <t>156785</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149869</t>
+          <t>143340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176327</t>
+          <t>168483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33407</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25367</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47557</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>22970</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16945</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31015</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,33%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36081</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>15736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50431</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>55997</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47066</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73524</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>126034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>87786</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135607</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>223393</t>
+          <t>212782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56993</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>49515</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63712</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>75450</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62303</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>90301</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>75,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64816</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56769</t>
+          <t>38738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72465</t>
+          <t>52993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>140266</t>
+          <t>103513</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126225</t>
+          <t>93776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159916</t>
+          <t>114014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23276</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16557</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30754</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>24468</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9617</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37615</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>24,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>32828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>49024</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>37821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63065</t>
+          <t>58059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80269</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>99918</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89372</t>
+          <t>71566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189290</t>
+          <t>151835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63332</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56388</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69849</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>71506</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65194</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>77592</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,36%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67415</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>62247</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74075</t>
+          <t>74420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>138922</t>
+          <t>132085</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128844</t>
+          <t>121724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147959</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20198</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13681</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27142</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17474</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11388</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23786</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30584</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>39708</t>
+          <t>38331</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>29540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49786</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>83530</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>88980</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89650</t>
+          <t>86886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178630</t>
+          <t>170416</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>253675</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>239906</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>273005</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>510709</t>
+          <t>461960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>560991</t>
+          <t>501963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97226</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>81998</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113809</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>77868</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>58538</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91637</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104460</t>
+          <t>79073</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88611</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123299</t>
+          <t>92123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>182328</t>
+          <t>176298</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>156770</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206982</t>
+          <t>196773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
